--- a/packages/adapter-ca-cslb/fixtures/contractors-master-sample.xlsx
+++ b/packages/adapter-ca-cslb/fixtures/contractors-master-sample.xlsx
@@ -4,40 +4,31 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Licenses" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="MasterLicenseData" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="79">
-  <si>
-    <t>License Number</t>
-  </si>
-  <si>
-    <t>Business Name</t>
-  </si>
-  <si>
-    <t>DBA Name</t>
-  </si>
-  <si>
-    <t>License Type</t>
-  </si>
-  <si>
-    <t>Classifications</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Issue Date</t>
-  </si>
-  <si>
-    <t>Expiration Date</t>
-  </si>
-  <si>
-    <t>Address</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="113">
+  <si>
+    <t>LicenseNo</t>
+  </si>
+  <si>
+    <t>LastUpdate</t>
+  </si>
+  <si>
+    <t>BusinessName</t>
+  </si>
+  <si>
+    <t>BUS-NAME-2</t>
+  </si>
+  <si>
+    <t>FullBusinessName</t>
+  </si>
+  <si>
+    <t>MailingAddress</t>
   </si>
   <si>
     <t>City</t>
@@ -46,64 +37,184 @@
     <t>State</t>
   </si>
   <si>
-    <t>Zip</t>
-  </si>
-  <si>
     <t>County</t>
   </si>
   <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>Personnel Name</t>
-  </si>
-  <si>
-    <t>Personnel Title</t>
+    <t>ZIPCode</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>BusinessPhone</t>
+  </si>
+  <si>
+    <t>BusinessType</t>
+  </si>
+  <si>
+    <t>IssueDate</t>
+  </si>
+  <si>
+    <t>ReissueDate</t>
+  </si>
+  <si>
+    <t>ExpirationDate</t>
+  </si>
+  <si>
+    <t>InactivationDate</t>
+  </si>
+  <si>
+    <t>ReactivationDate</t>
+  </si>
+  <si>
+    <t>PendingSuspension</t>
+  </si>
+  <si>
+    <t>PendingClassRemoval</t>
+  </si>
+  <si>
+    <t>PendingClassReplace</t>
+  </si>
+  <si>
+    <t>PrimaryStatus</t>
+  </si>
+  <si>
+    <t>SecondaryStatus</t>
+  </si>
+  <si>
+    <t>Classifications(s)</t>
+  </si>
+  <si>
+    <t>AsbestosReg</t>
+  </si>
+  <si>
+    <t>WorkersCompCoverageType</t>
+  </si>
+  <si>
+    <t>WCInsuranceCompany</t>
+  </si>
+  <si>
+    <t>WCPolicyNumber</t>
+  </si>
+  <si>
+    <t>WCEffectiveDate</t>
+  </si>
+  <si>
+    <t>WCExpirationDate</t>
+  </si>
+  <si>
+    <t>WCCancellationDate</t>
+  </si>
+  <si>
+    <t>WCSuspendDate</t>
+  </si>
+  <si>
+    <t>CBSuretyCompany</t>
+  </si>
+  <si>
+    <t>CBNumber</t>
+  </si>
+  <si>
+    <t>CBEffectiveDate</t>
+  </si>
+  <si>
+    <t>CBCancellationDate</t>
+  </si>
+  <si>
+    <t>CBAmount</t>
+  </si>
+  <si>
+    <t>WBSuretyCompany</t>
+  </si>
+  <si>
+    <t>WBNumber</t>
+  </si>
+  <si>
+    <t>WBEffectiveDate</t>
+  </si>
+  <si>
+    <t>WBCancellationDate</t>
+  </si>
+  <si>
+    <t>WBAmount</t>
+  </si>
+  <si>
+    <t>DBSuretyCompany</t>
+  </si>
+  <si>
+    <t>DBNumber</t>
+  </si>
+  <si>
+    <t>DBEffectiveDate</t>
+  </si>
+  <si>
+    <t>DBCancellationDate</t>
+  </si>
+  <si>
+    <t>DBAmount</t>
+  </si>
+  <si>
+    <t>DateRequired</t>
+  </si>
+  <si>
+    <t>DiscpCaseRegion</t>
+  </si>
+  <si>
+    <t>DBBondReason</t>
+  </si>
+  <si>
+    <t>DBCaseNo</t>
+  </si>
+  <si>
+    <t>NAME-TP-2</t>
   </si>
   <si>
     <t>1234567</t>
   </si>
   <si>
+    <t>06/28/2026</t>
+  </si>
+  <si>
     <t>Golden State Builders LLC</t>
   </si>
   <si>
+    <t>Golden State Construction</t>
+  </si>
+  <si>
+    <t>100 Market St</t>
+  </si>
+  <si>
+    <t>San Francisco</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>94105</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>4155550100</t>
+  </si>
+  <si>
+    <t>LLC</t>
+  </si>
+  <si>
+    <t>01/15/2019</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Contractor</t>
-  </si>
-  <si>
-    <t>A-General Engineering; B-General Building</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>01/15/2019</t>
-  </si>
-  <si>
     <t>12/31/2099</t>
   </si>
   <si>
-    <t>100 Market St</t>
-  </si>
-  <si>
-    <t>San Francisco</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>94105</t>
-  </si>
-  <si>
-    <t>4155550100</t>
-  </si>
-  <si>
-    <t>Jordan Lee</t>
-  </si>
-  <si>
-    <t>Qualifier</t>
+    <t>CLEAR</t>
+  </si>
+  <si>
+    <t>A;B</t>
   </si>
   <si>
     <t>2345678</t>
@@ -115,34 +226,31 @@
     <t>Pacific Roof Plus</t>
   </si>
   <si>
-    <t>C39-Roofing</t>
+    <t>200 Ocean Ave</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>90001</t>
+  </si>
+  <si>
+    <t>2135550100</t>
+  </si>
+  <si>
+    <t>Corporation</t>
+  </si>
+  <si>
+    <t>03/20/2018</t>
+  </si>
+  <si>
+    <t>06/30/2020</t>
   </si>
   <si>
     <t>Expired</t>
   </si>
   <si>
-    <t>03/20/2018</t>
-  </si>
-  <si>
-    <t>06/30/2020</t>
-  </si>
-  <si>
-    <t>200 Ocean Ave</t>
-  </si>
-  <si>
-    <t>Los Angeles</t>
-  </si>
-  <si>
-    <t>90001</t>
-  </si>
-  <si>
-    <t>2135550100</t>
-  </si>
-  <si>
-    <t>Casey Nguyen</t>
-  </si>
-  <si>
-    <t>RMO</t>
+    <t>C39</t>
   </si>
   <si>
     <t>3456789</t>
@@ -151,46 +259,64 @@
     <t>Central Valley Mechanical</t>
   </si>
   <si>
-    <t>C20-HVAC; C36-Plumbing</t>
-  </si>
-  <si>
-    <t>Suspended</t>
+    <t>300 Farm Rd</t>
+  </si>
+  <si>
+    <t>Fresno</t>
+  </si>
+  <si>
+    <t>93721</t>
+  </si>
+  <si>
+    <t>5595550100</t>
   </si>
   <si>
     <t>07/01/2021</t>
   </si>
   <si>
-    <t>300 Farm Rd</t>
-  </si>
-  <si>
-    <t>Fresno</t>
-  </si>
-  <si>
-    <t>93721</t>
-  </si>
-  <si>
-    <t>5595550100</t>
-  </si>
-  <si>
-    <t>Riley Patel</t>
-  </si>
-  <si>
-    <t>Officer</t>
+    <t>Work Comp Susp</t>
+  </si>
+  <si>
+    <t>C20;C36</t>
   </si>
   <si>
     <t>4567890</t>
   </si>
   <si>
-    <t>Sierra Solar Works</t>
-  </si>
-  <si>
-    <t>C46-Solar</t>
-  </si>
-  <si>
-    <t>05/10/2022</t>
-  </si>
-  <si>
-    <t>400 Pine Rd</t>
+    <t>Desert Solar Works</t>
+  </si>
+  <si>
+    <t>400 Sun Rd</t>
+  </si>
+  <si>
+    <t>Palm Springs</t>
+  </si>
+  <si>
+    <t>Riverside</t>
+  </si>
+  <si>
+    <t>92262</t>
+  </si>
+  <si>
+    <t>7605550100</t>
+  </si>
+  <si>
+    <t>Sole Owner</t>
+  </si>
+  <si>
+    <t>05/05/2022</t>
+  </si>
+  <si>
+    <t>C46</t>
+  </si>
+  <si>
+    <t>5678901</t>
+  </si>
+  <si>
+    <t>Unmapped Specialty</t>
+  </si>
+  <si>
+    <t>500 New Ave</t>
   </si>
   <si>
     <t>Sacramento</t>
@@ -202,52 +328,28 @@
     <t>9165550100</t>
   </si>
   <si>
-    <t>Alex Morgan</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Golden State Builders LLC Branch</t>
-  </si>
-  <si>
-    <t>B-General Building</t>
-  </si>
-  <si>
-    <t>500 Mission St</t>
-  </si>
-  <si>
-    <t>4155550199</t>
-  </si>
-  <si>
-    <t>5678901</t>
-  </si>
-  <si>
-    <t>Unknown Specialty Co</t>
-  </si>
-  <si>
-    <t>Z99-Unmapped</t>
-  </si>
-  <si>
-    <t>Mystery</t>
-  </si>
-  <si>
-    <t>09/09/2020</t>
-  </si>
-  <si>
-    <t>600 Desert Way</t>
-  </si>
-  <si>
-    <t>San Diego</t>
-  </si>
-  <si>
-    <t>92101</t>
-  </si>
-  <si>
-    <t>6195550100</t>
-  </si>
-  <si>
-    <t>Sam Rivera</t>
+    <t>Partnership</t>
+  </si>
+  <si>
+    <t>08/08/2023</t>
+  </si>
+  <si>
+    <t>MYSTERY</t>
+  </si>
+  <si>
+    <t>Z99</t>
+  </si>
+  <si>
+    <t>Golden State Builders Duplicate</t>
+  </si>
+  <si>
+    <t>101 Market St</t>
+  </si>
+  <si>
+    <t>4155550101</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -624,10 +726,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -676,304 +778,1060 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="P2" t="s">
-        <v>30</v>
+        <v>65</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>64</v>
+      </c>
+      <c r="R2" t="s">
+        <v>64</v>
+      </c>
+      <c r="S2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" t="s">
+        <v>64</v>
+      </c>
+      <c r="U2" t="s">
+        <v>64</v>
+      </c>
+      <c r="V2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="L3" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="N3" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="O3" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="P3" t="s">
-        <v>43</v>
+        <v>77</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>64</v>
+      </c>
+      <c r="R3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S3" t="s">
+        <v>64</v>
+      </c>
+      <c r="T3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U3" t="s">
+        <v>64</v>
+      </c>
+      <c r="V3" t="s">
+        <v>78</v>
+      </c>
+      <c r="W3" t="s">
+        <v>64</v>
+      </c>
+      <c r="X3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="J4" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="L4" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N4" t="s">
+        <v>86</v>
+      </c>
+      <c r="O4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>64</v>
+      </c>
+      <c r="R4" t="s">
+        <v>64</v>
+      </c>
+      <c r="S4" t="s">
+        <v>64</v>
+      </c>
+      <c r="T4" t="s">
+        <v>64</v>
+      </c>
+      <c r="U4" t="s">
+        <v>64</v>
+      </c>
+      <c r="V4" t="s">
+        <v>87</v>
+      </c>
+      <c r="W4" t="s">
+        <v>64</v>
+      </c>
+      <c r="X4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" t="s">
+        <v>95</v>
+      </c>
+      <c r="M5" t="s">
+        <v>96</v>
+      </c>
+      <c r="N5" t="s">
+        <v>97</v>
+      </c>
+      <c r="O5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>64</v>
+      </c>
+      <c r="R5" t="s">
+        <v>64</v>
+      </c>
+      <c r="S5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T5" t="s">
+        <v>64</v>
+      </c>
+      <c r="U5" t="s">
+        <v>64</v>
+      </c>
+      <c r="V5" t="s">
+        <v>66</v>
+      </c>
+      <c r="W5" t="s">
+        <v>64</v>
+      </c>
+      <c r="X5" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" t="s">
+        <v>102</v>
+      </c>
+      <c r="J6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M6" t="s">
+        <v>105</v>
+      </c>
+      <c r="N6" t="s">
+        <v>106</v>
+      </c>
+      <c r="O6" t="s">
+        <v>64</v>
+      </c>
+      <c r="P6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>64</v>
+      </c>
+      <c r="R6" t="s">
+        <v>64</v>
+      </c>
+      <c r="S6" t="s">
+        <v>64</v>
+      </c>
+      <c r="T6" t="s">
+        <v>64</v>
+      </c>
+      <c r="U6" t="s">
+        <v>64</v>
+      </c>
+      <c r="V6" t="s">
+        <v>107</v>
+      </c>
+      <c r="W6" t="s">
+        <v>64</v>
+      </c>
+      <c r="X6" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>52</v>
       </c>
-      <c r="O4" t="s">
+      <c r="B7" t="s">
         <v>53</v>
       </c>
-      <c r="P4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="C7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" t="s">
         <v>57</v>
       </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="H7" t="s">
         <v>58</v>
       </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="I7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" t="s">
         <v>59</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K7" t="s">
         <v>60</v>
       </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" t="s">
-        <v>60</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="L7" t="s">
+        <v>111</v>
+      </c>
+      <c r="M7" t="s">
         <v>62</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N7" t="s">
         <v>63</v>
       </c>
-      <c r="P5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="O7" t="s">
+        <v>64</v>
+      </c>
+      <c r="P7" t="s">
         <v>65</v>
       </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="Q7" t="s">
+        <v>64</v>
+      </c>
+      <c r="R7" t="s">
+        <v>64</v>
+      </c>
+      <c r="S7" t="s">
+        <v>64</v>
+      </c>
+      <c r="T7" t="s">
+        <v>64</v>
+      </c>
+      <c r="U7" t="s">
+        <v>64</v>
+      </c>
+      <c r="V7" t="s">
         <v>66</v>
       </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" t="s">
-        <v>68</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
-      </c>
-      <c r="P6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s">
-        <v>75</v>
-      </c>
-      <c r="K7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" t="s">
-        <v>76</v>
-      </c>
-      <c r="M7" t="s">
-        <v>75</v>
-      </c>
-      <c r="N7" t="s">
-        <v>77</v>
-      </c>
-      <c r="O7" t="s">
-        <v>78</v>
-      </c>
-      <c r="P7" t="s">
+      <c r="W7" t="s">
+        <v>64</v>
+      </c>
+      <c r="X7" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ7" t="s">
         <v>64</v>
       </c>
     </row>
